--- a/daily_matches/job_matches_2026-09-22.xlsx
+++ b/daily_matches/job_matches_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Aledade</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>RAG, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947423e1243398ca</t>
+          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, S3, EC2, Data Lake, CI/CD, Databricks, PySpark, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f9f03cfec0fc88</t>
+          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Tableau, Power BI</t>
+          <t>AI Engineer, RAG, Gemini, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad676d0583954a5</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce71e7dde10807</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Security Engineer- Remote (Anywhere in the U.S.)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GuidePoint Security</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b258636181c4da88</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Intern – AI Engineer, Enterprise AI &amp; Workflow Automation – Plymouth, MN – Summer 2027</t>
+          <t>Sr AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Connection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plymouth, MN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Power BI, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b9555ed0046695</t>
+          <t>https://www.indeed.com/viewjob?jk=58eb29d3b2a7a928</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mgr Data Science</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Southwire</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Keras, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Keras, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f7f0d4317cea21</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b2706dfa15be8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Primerica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R</t>
+          <t>Data Scientist, RAG, AWS SageMaker, Data Lake, Kubernetes, Terraform, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca66092b92677d70</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa2fd922bb47b39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Scientist Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Devengine</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c6cb0948cf8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=044eacd7359d999d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Robot Perception</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Azure ML, Synapse, Data Lake, GitHub Actions, Git, R, Scala, A/B Testing</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Snowflake, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633be495dda3ee56</t>
+          <t>https://www.indeed.com/viewjob?jk=46a5c793938dacf2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae5a91c56b094aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c3095638ea165d6a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CGP / Gemini Enterprise Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Snowflake, BigQuery, Python, R</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ded3262648b12f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a948ab315164b6b1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HPC SYSTEMS ENGINEER</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Git, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a468560cb8abd5</t>
+          <t>https://www.indeed.com/viewjob?jk=adb6a6278fff5e9a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Summer 2027 Intern: Data Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Glue, Redshift, Git, Snowflake, Databricks, Redshift, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0022787a9f1c8382</t>
+          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Chorus</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Kafka, NoSQL, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4465259f3fa73c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa6f62102fbec4d6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) - Applied AI</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea6ca493749797f</t>
+          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer - Production Security</t>
+          <t>Associate AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Connection</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, Power BI, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0de66920c6dcd3ec</t>
+          <t>https://www.indeed.com/viewjob?jk=21e5517cf4cbbef6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer - Production Security</t>
+          <t>Machine Learning Science Intern - Summer 2027</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, PyTorch, Docker, Git, PySpark, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327fc293963d72d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3639279c734d87ed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer - Production Security</t>
+          <t>Senior Database Administrator / Data Engineer - SQL Server</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Redshift, Redshift, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc49fe05a554201e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b8598ba79e5eba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer - Production Security</t>
+          <t>Senior Database Administrator / Data Engineer - PostgreSQL / MySQL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Redshift, Redshift, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07544521dd0a6fab</t>
+          <t>https://www.indeed.com/viewjob?jk=7f606e8f0a4957ef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Oxipital AI</t>
+          <t>Relativity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PyTorch, OpenCV, S3, EC2, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Copilot, Kubernetes, AKS, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87f66e10feaf0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=055ff8b89337838c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aquila Technology</t>
+          <t>Infoblox</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Tacoma, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S3, EC2, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13b02f1ea5b9b74</t>
+          <t>https://www.indeed.com/viewjob?jk=d0939386aa8929b6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Investment Risk Senior Associate - Data Science/ Applied AI ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Tableau, Power BI, Python, R</t>
+          <t>RAG, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d023f201ae43801a</t>
+          <t>https://www.indeed.com/viewjob?jk=861ebe4aff56879f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,427 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b74c54d80c45a98</t>
+          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer - Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rubrik</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=747845470f893d14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fd3ccc7d244fa4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data and AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CDM Smith</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cb996fda4d3304d</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - C# AND Dotnet</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Finastra</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78a084f9c9d28015</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Symbotic</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01eb87192a7c241b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Java Developer - Cyber Security Authentication</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39a99693cdec1808</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. Manger, Product Management-ROCm AI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc7263c694fc3cce</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer - Internal Applications</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hermeus</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc6be0cd3471f632</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Joby Aviation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Carlos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64203a99715fd974</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Evans Transportation Services</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Delafield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Varonis Systems</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Hugging Face, Prompt Engineering, Databricks, PySpark, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1a19748fcb818cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Decision Analytics, Store Operations Transformation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e78e82af59e07d1f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-22.xlsx
+++ b/daily_matches/job_matches_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
+          <t>Senior AI Engineer - US</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aledade</t>
+          <t>Typeform</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,33 +482,33 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Data Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Data Lake, CI/CD, Databricks, PySpark, MySQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, LLaMA, Pinecone, Glue, Redshift, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc3d67e2533b3c1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Fusemachines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, Copilot, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce71e7dde10807</t>
+          <t>https://www.indeed.com/viewjob?jk=515f6314cbbd1a5a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d16afaf22f8607c6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr AI Solutions Engineer</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58eb29d3b2a7a928</t>
+          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Part Time Teller (20 Hours), Castro Branch</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Southwire</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Keras, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b2706dfa15be8</t>
+          <t>https://www.indeed.com/viewjob?jk=62e481a61bf24644</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer 4 (Python, AWS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primerica</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, Data Lake, Kubernetes, Terraform, Tableau, Power BI, Python, R</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa2fd922bb47b39</t>
+          <t>https://www.indeed.com/viewjob?jk=6785ed8543590d56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist Intern</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=044eacd7359d999d</t>
+          <t>https://www.indeed.com/viewjob?jk=30216af3fb095a16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Robot Perception</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Snowflake, Python, SQL, R, Optimization</t>
+          <t>LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a5c793938dacf2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Agentic AI Developer IV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3095638ea165d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f07a613da61c33e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a948ab315164b6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd0eafd97ddc943</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb6a6278fff5e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=96810a7a6dbdd75a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern: Data Engineering</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Live Oak Bank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Git, Snowflake, Databricks, Redshift, Kafka, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae77aaad96ec33c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa6f62102fbec4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c69033d42d38292e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
+          <t>https://www.indeed.com/viewjob?jk=42eb97c80e2c8216</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate AI Solutions Engineer</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, Power BI, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e5517cf4cbbef6</t>
+          <t>https://www.indeed.com/viewjob?jk=accc0a915fc209c5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Science Intern - Summer 2027</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Docker, Git, PySpark, Python, SQL, R, Scala, A/B Testing</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3639279c734d87ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b3b1fc7d47dc22fc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Database Administrator / Data Engineer - SQL Server</t>
+          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Redshift, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b8598ba79e5eba</t>
+          <t>https://www.indeed.com/viewjob?jk=92d161b705c196d3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Database Administrator / Data Engineer - PostgreSQL / MySQL</t>
+          <t>Full Stack Engineer 4 (Java, AWS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Redshift, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f606e8f0a4957ef</t>
+          <t>https://www.indeed.com/viewjob?jk=0307bf553f12270f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Relativity</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, AKS, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055ff8b89337838c</t>
+          <t>https://www.indeed.com/viewjob?jk=4043d02ce95e238a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infoblox</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tacoma, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0939386aa8929b6</t>
+          <t>https://www.indeed.com/viewjob?jk=24beeb2eb3b965af</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861ebe4aff56879f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b76875b0de3a36</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd502d8d46c80b1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud Infrastructure</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747845470f893d14</t>
+          <t>https://www.indeed.com/viewjob?jk=afd7b2b83e756812</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd3ccc7d244fa4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2125e052c84e5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data and AI Solution Architect</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CDM Smith</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Databricks, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cb996fda4d3304d</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf5c97e77c90b18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - C# AND Dotnet</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Finastra</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a084f9c9d28015</t>
+          <t>https://www.indeed.com/viewjob?jk=5275118ed12fd241</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01eb87192a7c241b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Java Developer - Cyber Security Authentication</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a99693cdec1808</t>
+          <t>https://www.indeed.com/viewjob?jk=9b405211329b437c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Manger, Product Management-ROCm AI</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7263c694fc3cce</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae0177c68a80ad9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - Internal Applications</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6be0cd3471f632</t>
+          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Full-stack Engineer 4 (Python, Typescript)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64203a99715fd974</t>
+          <t>https://www.indeed.com/viewjob?jk=8f31e7024946559a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c00cdc257f308304</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hugging Face, Prompt Engineering, Databricks, PySpark, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,42 +1651,1162 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19748fcb818cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8d78256053c3dc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Decision Analytics, Store Operations Transformation</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa38f701dd207fff</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7597fda19c9e29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18346eea91456b61</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sentara</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Norfolk, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, MLflow, Kubernetes, AKS, CI/CD, Terraform, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Machine Learning Platform</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kubernetes, CI/CD, Dask, Python, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ce796de85a39f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=382e3897813d90d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Applied AI and Agentic Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>VSP Vision</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Cortex, Snowflake, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54f5bda027b38d6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winsor Consulting Group, LLC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Iowa City, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2985e553c18ec3db</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Winsor Consulting Group, LLC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tucson, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1325ecaac5c44cad</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Winsor Consulting Group, LLC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Buffalo, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c64761d43f50c4ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer Data &amp; AI I (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Hadoop, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a520a8863e5efb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8797055dc68a25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=743e32eaa52b72c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c255b12c34f0c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>React Web Developer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D51" t="n">
         <v>10</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e78e82af59e07d1f</t>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31229f9885d5fb8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE) - Applied AI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2c89571c6127f09</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Databricks, PySpark, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39e65aefb15b68ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8858a80ff362d8be</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>React Web Developer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce593aca419f40c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE) - Applied AI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e2da2b5eeb07a03</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ThredUp</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Kafka, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c0a1a993f9ad4af</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Intern - Probe Manufacturing Engineering (Probe AME)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51993810c0f9426f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Gemini, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6e6080b6ae5a547</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ConstructConnect</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bb34334df8ad751</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4, Enterprise CI/CD (AWS, Python, Groovy)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd077bfd22709745</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4, Enterprise CI/CD (AWS, Python, Groovy</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ac6d8e173d6cf12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 5 (ATM)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe710fe27e77cee5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Innova Software Services</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Copilot, Pinecone, Prompt Engineering, S3, EC2, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9df5f5453def4438</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RS Americas</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=361ed98ae3fe9314</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>IT Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Scot Forge</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Spring Grove, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Generative AI, Polars, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07e14ce48a7f7703</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern - MN, CO</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Xcel Energy</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, PyTorch, Git, Databricks, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a02cff4acb0835f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern - MN, CO</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Xcel Energy</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, PyTorch, Git, Databricks, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10f324a128cee047</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-22.xlsx
+++ b/daily_matches/job_matches_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Architect with AI &amp; Agentic Systems</t>
+          <t>Senior Database Engineer- Arlington, VA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, S3, Docker, Kubernetes</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4542de43b1262402</t>
+          <t>https://www.indeed.com/viewjob?jk=61eae97728d8e35d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agentic AI Databricks</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Data Lake, MLflow, Git, Databricks</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, GCP Vertex AI, BigQuery, Dataflow, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=159ff5be89845750</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Databricks &amp; Agentic AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Coca Cola Southwest Beverages</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, PySpark</t>
+          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f627225261b22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Observability SRE (Site Reliability Engineer)</t>
+          <t>Software Engineer 2 (Gen AI, LLM, Spring Boot)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bdc78152906707</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab40f0fb4a43c1e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Software Engineer 2 (Gen AI, LLM, Spring Boot)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab165c224f9bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=b327e81664e3144a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Client Delivery Architecture</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NUVISTA AI</t>
+          <t>Oshkosh Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, Redshift</t>
+          <t>RAG, Redshift, Synapse, Data Lake, AKS, Terraform, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b11276c05726f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Copilot, S3, EC2, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=286cf2909fa4ccd8</t>
+          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Hugging Face, Prompt Engineering, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0de69679a365a1e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Nuuly - Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Nuuly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, SQL, R, Java</t>
+          <t>Data Scientist, TensorFlow, PyTorch, BigQuery, MLflow, Kubernetes, BigQuery, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
+          <t>https://www.indeed.com/viewjob?jk=306c2a46ae23f5a2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HPC Windows Server Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Synapse, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518ee0c62a254d22</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>evolutio</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Synapse, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab80761667bcf597</t>
+          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Security Engineer II (Defensive Operations)</t>
+          <t>Senior Data/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Flywire</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,1512 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5106607fa3d28a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5fae1eed697d12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexamp</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Seek Now</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bitsight</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Boston, MA, US USA</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Hadoop, NoSQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63f33f26ef49d2e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 5 (Java, AWS, Kafka)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Riverwoods, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df64f895efc7335d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b86963fc0b12544</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aimpoint Digital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, FastAPI, Kubernetes, CI/CD, Git, Snowflake, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Cloud and Analytics platform</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Macquarie Group</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Dask, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a255f0dfec925d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=903dd015fa528592</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=380316b9e0c92c7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Burr Ridge, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7973fc7366d1ef95</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6e4280958473ee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Test Automation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0523cd5542a3a484</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Activated Insights</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>S3, Kubernetes, CI/CD, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Activated Insights</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Idaho Falls, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>S3, Kubernetes, CI/CD, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Databricks Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Intern- Robot Perception</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Symbotic</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Snowflake, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faaa5339006c4284</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Developer III - AI Services</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4052da48e533b8a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer-5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fcc298a65fe517f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RWE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Platform Engineer (Software Engineer II/III)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Multi Media LLC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b6373038703f903</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NBME</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=195d724701bfe29e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4af88c030f9ccd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Allegion</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, CI/CD, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d6a8325afc1b14d</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cloud Senior Software Developer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97acb4c67250c28a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SBA Communications</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Dataflow, CI/CD, Git, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b33ca6716f51741</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=477e0e32b1cfd7aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>In-Vehicle Network Software Developer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Allen Park, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a4614eb3f6f8050</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f377f281708fe1d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69fe41d57f71b353</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=873b0eb03be3ffef</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Architect (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Xceleration Partners LLC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad36e6da08bd6e32</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d03f8606ddaab60</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Fullstack Python/AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1667c5a41c5f093</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Winnebago Industries, Inc.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=844bcfbfc6def1db</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer Fullstack / Backend II (Full Time) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ba4b2afd8ba9573</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Intern- Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Symbotic</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5486700e70c83dde</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DevOps and Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sunbird Software Inc.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a084932bbeae091</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Engineer – Application</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Federated Hermes</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Warrendale, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, CI/CD, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rhombus Power</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc6cd2be14b558e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Bally's Interactive</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=657d2500de079e56</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Cortex, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59a0f7ce14ba21c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Decision Scientist</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Reyes Coca-Cola Bottling</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Niles, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Azure ML, MLflow, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72ec20c373c8c642</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>The New York Times</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, CI/CD, Terraform, Git, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f25177f1135efd1f</t>
         </is>
       </c>
     </row>
